--- a/backend/data/financials_by_company/1832.HK.xlsx
+++ b/backend/data/financials_by_company/1832.HK.xlsx
@@ -687,61 +687,61 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-934.437398</v>
+        <v>9207.759700000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000262</v>
+        <v>0.146155</v>
       </c>
       <c r="D2" t="n">
-        <v>269000</v>
+        <v>-1739000</v>
       </c>
       <c r="E2" t="n">
-        <v>-3566000</v>
+        <v>63000</v>
       </c>
       <c r="F2" t="n">
-        <v>-3566000</v>
+        <v>63000</v>
       </c>
       <c r="G2" t="n">
-        <v>-18955000</v>
+        <v>-5952000</v>
       </c>
       <c r="H2" t="n">
-        <v>11152000</v>
+        <v>4538000</v>
       </c>
       <c r="I2" t="n">
-        <v>21583000</v>
+        <v>9943000</v>
       </c>
       <c r="J2" t="n">
-        <v>-3297000</v>
+        <v>-1676000</v>
       </c>
       <c r="K2" t="n">
-        <v>-14449000</v>
+        <v>-6214000</v>
       </c>
       <c r="L2" t="n">
-        <v>-4627000</v>
+        <v>-944000</v>
       </c>
       <c r="M2" t="n">
-        <v>4632000</v>
+        <v>977000</v>
       </c>
       <c r="N2" t="n">
-        <v>5000</v>
+        <v>33000</v>
       </c>
       <c r="O2" t="n">
-        <v>-15389934.437398</v>
+        <v>-6005792.2403</v>
       </c>
       <c r="P2" t="n">
-        <v>-18955000</v>
+        <v>-5952000</v>
       </c>
       <c r="Q2" t="n">
-        <v>53681000</v>
+        <v>26103000</v>
       </c>
       <c r="R2" t="n">
-        <v>1022000</v>
+        <v>530000</v>
       </c>
       <c r="S2" t="n">
-        <v>-14454000</v>
+        <v>-6247000</v>
       </c>
       <c r="T2" t="n">
         <v>360000000</v>
@@ -750,145 +750,157 @@
         <v>360000000</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.053</v>
+        <v>-0.017</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.053</v>
+        <v>-0.017</v>
       </c>
       <c r="X2" t="n">
-        <v>-18955000</v>
+        <v>-5952000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-18955000</v>
+        <v>-5952000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-18955000</v>
+        <v>-5952000</v>
       </c>
       <c r="AB2" t="n">
+        <v>188000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-6140000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-6140000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-1051000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-7191000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>88000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-88000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>1409000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-944000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>977000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-6302000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>16160000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>16102000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4538000</v>
+      </c>
+      <c r="AR2" t="n">
         <v>121000</v>
       </c>
-      <c r="AC2" t="n">
-        <v>-19076000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-19076000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-5000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-19081000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-3566000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-3000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-115000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3684000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-4627000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>4632000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-10886000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>32098000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>32054000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>4417000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1161000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>41000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>530000</v>
+      </c>
       <c r="AX2" t="n">
-        <v>21212000</v>
+        <v>9858000</v>
       </c>
       <c r="AY2" t="n">
-        <v>21583000</v>
+        <v>9943000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>42795000</v>
+        <v>19801000</v>
       </c>
       <c r="BA2" t="n">
-        <v>42795000</v>
+        <v>19801000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>241.935484</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004032</v>
+        <v>0.164559</v>
       </c>
       <c r="D3" t="n">
-        <v>-7373000</v>
+        <v>-8133000</v>
       </c>
       <c r="E3" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-22961000</v>
+        <v>-11425000</v>
       </c>
       <c r="H3" t="n">
-        <v>10865000</v>
+        <v>4306000</v>
       </c>
       <c r="I3" t="n">
-        <v>23665000</v>
+        <v>12601000</v>
       </c>
       <c r="J3" t="n">
-        <v>-7313000</v>
+        <v>-8133000</v>
       </c>
       <c r="K3" t="n">
-        <v>-18178000</v>
+        <v>-12439000</v>
       </c>
       <c r="L3" t="n">
-        <v>-4881000</v>
+        <v>-1286000</v>
       </c>
       <c r="M3" t="n">
-        <v>4886000</v>
+        <v>1319000</v>
       </c>
       <c r="N3" t="n">
-        <v>5000</v>
+        <v>33000</v>
       </c>
       <c r="O3" t="n">
-        <v>-23020758.064516</v>
+        <v>-11425000</v>
       </c>
       <c r="P3" t="n">
-        <v>-22961000</v>
+        <v>-11425000</v>
       </c>
       <c r="Q3" t="n">
-        <v>55092000</v>
+        <v>28225000</v>
       </c>
       <c r="R3" t="n">
-        <v>1029000</v>
+        <v>786000</v>
       </c>
       <c r="S3" t="n">
-        <v>-18183000</v>
+        <v>-12472000</v>
       </c>
       <c r="T3" t="n">
         <v>360000000</v>
@@ -897,145 +909,143 @@
         <v>360000000</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.064</v>
+        <v>-0.032</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.064</v>
+        <v>-0.032</v>
       </c>
       <c r="X3" t="n">
-        <v>-22961000</v>
+        <v>-11425000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-22961000</v>
+        <v>-11425000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-22961000</v>
+        <v>-11425000</v>
       </c>
       <c r="AB3" t="n">
-        <v>10000</v>
+        <v>69000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-22971000</v>
+        <v>-11494000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-22971000</v>
+        <v>-11494000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-93000</v>
+        <v>-2264000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-23064000</v>
+        <v>-13758000</v>
       </c>
       <c r="AG3" t="n">
-        <v>60000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-60000</v>
-      </c>
-      <c r="AI3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>-4881000</v>
+        <v>-1286000</v>
       </c>
       <c r="AL3" t="n">
-        <v>4886000</v>
+        <v>1319000</v>
       </c>
       <c r="AM3" t="n">
-        <v>5000</v>
+        <v>33000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-18245000</v>
+        <v>-12474000</v>
       </c>
       <c r="AO3" t="n">
-        <v>31427000</v>
+        <v>15624000</v>
       </c>
       <c r="AP3" t="n">
-        <v>31378000</v>
+        <v>15624000</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>3895000</v>
+      </c>
       <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>3895000</v>
+      </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>13182000</v>
+        <v>3150000</v>
       </c>
       <c r="AY3" t="n">
-        <v>23665000</v>
+        <v>12601000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>36847000</v>
+        <v>15751000</v>
       </c>
       <c r="BA3" t="n">
-        <v>36847000</v>
+        <v>15751000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>241.935484</v>
       </c>
       <c r="C4" t="n">
-        <v>0.164559</v>
+        <v>0.004032</v>
       </c>
       <c r="D4" t="n">
-        <v>-8133000</v>
+        <v>-7373000</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="G4" t="n">
-        <v>-11425000</v>
+        <v>-22961000</v>
       </c>
       <c r="H4" t="n">
-        <v>4306000</v>
+        <v>10865000</v>
       </c>
       <c r="I4" t="n">
-        <v>12601000</v>
+        <v>23665000</v>
       </c>
       <c r="J4" t="n">
-        <v>-8133000</v>
+        <v>-7313000</v>
       </c>
       <c r="K4" t="n">
-        <v>-12439000</v>
+        <v>-18178000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1286000</v>
+        <v>-4881000</v>
       </c>
       <c r="M4" t="n">
-        <v>1319000</v>
+        <v>4886000</v>
       </c>
       <c r="N4" t="n">
-        <v>33000</v>
+        <v>5000</v>
       </c>
       <c r="O4" t="n">
-        <v>-11425000</v>
+        <v>-23020758.064516</v>
       </c>
       <c r="P4" t="n">
-        <v>-11425000</v>
+        <v>-22961000</v>
       </c>
       <c r="Q4" t="n">
-        <v>28225000</v>
+        <v>55092000</v>
       </c>
       <c r="R4" t="n">
-        <v>786000</v>
+        <v>1029000</v>
       </c>
       <c r="S4" t="n">
-        <v>-12472000</v>
+        <v>-18183000</v>
       </c>
       <c r="T4" t="n">
         <v>360000000</v>
@@ -1044,143 +1054,145 @@
         <v>360000000</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.032</v>
+        <v>-0.064</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.032</v>
+        <v>-0.064</v>
       </c>
       <c r="X4" t="n">
-        <v>-11425000</v>
+        <v>-22961000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-11425000</v>
+        <v>-22961000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-11425000</v>
+        <v>-22961000</v>
       </c>
       <c r="AB4" t="n">
-        <v>69000</v>
+        <v>10000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-11494000</v>
+        <v>-22971000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-11494000</v>
+        <v>-22971000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2264000</v>
+        <v>-93000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-13758000</v>
+        <v>-23064000</v>
       </c>
       <c r="AG4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-60000</v>
+      </c>
+      <c r="AI4" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
       <c r="AK4" t="n">
-        <v>-1286000</v>
+        <v>-4881000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1319000</v>
+        <v>4886000</v>
       </c>
       <c r="AM4" t="n">
-        <v>33000</v>
+        <v>5000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-12474000</v>
+        <v>-18245000</v>
       </c>
       <c r="AO4" t="n">
-        <v>15624000</v>
+        <v>31427000</v>
       </c>
       <c r="AP4" t="n">
-        <v>15624000</v>
+        <v>31378000</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="n">
-        <v>3895000</v>
-      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>3895000</v>
-      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>3150000</v>
+        <v>13182000</v>
       </c>
       <c r="AY4" t="n">
-        <v>12601000</v>
+        <v>23665000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15751000</v>
+        <v>36847000</v>
       </c>
       <c r="BA4" t="n">
-        <v>15751000</v>
+        <v>36847000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>9207.759700000001</v>
+        <v>-934.437398</v>
       </c>
       <c r="C5" t="n">
-        <v>0.146155</v>
+        <v>0.000262</v>
       </c>
       <c r="D5" t="n">
-        <v>-1739000</v>
+        <v>269000</v>
       </c>
       <c r="E5" t="n">
-        <v>63000</v>
+        <v>-3566000</v>
       </c>
       <c r="F5" t="n">
-        <v>63000</v>
+        <v>-3566000</v>
       </c>
       <c r="G5" t="n">
-        <v>-5952000</v>
+        <v>-18955000</v>
       </c>
       <c r="H5" t="n">
-        <v>4538000</v>
+        <v>11152000</v>
       </c>
       <c r="I5" t="n">
-        <v>9943000</v>
+        <v>21583000</v>
       </c>
       <c r="J5" t="n">
-        <v>-1676000</v>
+        <v>-3297000</v>
       </c>
       <c r="K5" t="n">
-        <v>-6214000</v>
+        <v>-14449000</v>
       </c>
       <c r="L5" t="n">
-        <v>-944000</v>
+        <v>-4627000</v>
       </c>
       <c r="M5" t="n">
-        <v>977000</v>
+        <v>4632000</v>
       </c>
       <c r="N5" t="n">
-        <v>33000</v>
+        <v>5000</v>
       </c>
       <c r="O5" t="n">
-        <v>-6005792.2403</v>
+        <v>-15389934.437398</v>
       </c>
       <c r="P5" t="n">
-        <v>-5952000</v>
+        <v>-18955000</v>
       </c>
       <c r="Q5" t="n">
-        <v>26103000</v>
+        <v>53681000</v>
       </c>
       <c r="R5" t="n">
-        <v>530000</v>
+        <v>1022000</v>
       </c>
       <c r="S5" t="n">
-        <v>-6247000</v>
+        <v>-14454000</v>
       </c>
       <c r="T5" t="n">
         <v>360000000</v>
@@ -1189,98 +1201,86 @@
         <v>360000000</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.017</v>
+        <v>-0.053</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.017</v>
+        <v>-0.053</v>
       </c>
       <c r="X5" t="n">
-        <v>-5952000</v>
+        <v>-18955000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-5952000</v>
+        <v>-18955000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-5952000</v>
+        <v>-18955000</v>
       </c>
       <c r="AB5" t="n">
-        <v>188000</v>
+        <v>121000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-6140000</v>
+        <v>-19076000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-6140000</v>
+        <v>-19076000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1051000</v>
+        <v>-5000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-7191000</v>
+        <v>-19081000</v>
       </c>
       <c r="AG5" t="n">
-        <v>88000</v>
+        <v>-3566000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-88000</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>-3000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-115000</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>1409000</v>
+        <v>3684000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-944000</v>
+        <v>-4627000</v>
       </c>
       <c r="AL5" t="n">
-        <v>977000</v>
+        <v>4632000</v>
       </c>
       <c r="AM5" t="n">
-        <v>33000</v>
+        <v>5000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-6302000</v>
+        <v>-10886000</v>
       </c>
       <c r="AO5" t="n">
-        <v>16160000</v>
+        <v>32098000</v>
       </c>
       <c r="AP5" t="n">
-        <v>16102000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>4538000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>121000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4417000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1161000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>41000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>530000</v>
-      </c>
+        <v>32054000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>9858000</v>
+        <v>21212000</v>
       </c>
       <c r="AY5" t="n">
-        <v>9943000</v>
+        <v>21583000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19801000</v>
+        <v>42795000</v>
       </c>
       <c r="BA5" t="n">
-        <v>19801000</v>
+        <v>42795000</v>
       </c>
     </row>
   </sheetData>
@@ -1601,7 +1601,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>360000000</v>
@@ -1610,43 +1610,43 @@
         <v>360000000</v>
       </c>
       <c r="D2" t="n">
-        <v>74235000</v>
+        <v>8923000</v>
       </c>
       <c r="E2" t="n">
-        <v>93963000</v>
+        <v>37299000</v>
       </c>
       <c r="F2" t="n">
-        <v>34413000</v>
+        <v>85836000</v>
       </c>
       <c r="G2" t="n">
-        <v>111878000</v>
+        <v>102944000</v>
       </c>
       <c r="H2" t="n">
-        <v>-44095000</v>
+        <v>-5290000</v>
       </c>
       <c r="I2" t="n">
-        <v>34413000</v>
+        <v>85836000</v>
       </c>
       <c r="J2" t="n">
-        <v>16536000</v>
+        <v>20299000</v>
       </c>
       <c r="K2" t="n">
-        <v>34451000</v>
+        <v>85944000</v>
       </c>
       <c r="L2" t="n">
-        <v>66693000</v>
+        <v>85944000</v>
       </c>
       <c r="M2" t="n">
-        <v>33978000</v>
+        <v>85671000</v>
       </c>
       <c r="N2" t="n">
-        <v>-473000</v>
+        <v>-273000</v>
       </c>
       <c r="O2" t="n">
-        <v>34451000</v>
+        <v>85944000</v>
       </c>
       <c r="P2" t="n">
-        <v>-37822000</v>
+        <v>15519000</v>
       </c>
       <c r="Q2" t="n">
         <v>38122000</v>
@@ -1658,133 +1658,133 @@
         <v>461000</v>
       </c>
       <c r="T2" t="n">
-        <v>106136000</v>
+        <v>51157000</v>
       </c>
       <c r="U2" t="n">
-        <v>48112000</v>
+        <v>18760000</v>
       </c>
       <c r="V2" t="n">
-        <v>48112000</v>
+        <v>18760000</v>
       </c>
       <c r="W2" t="n">
-        <v>15870000</v>
+        <v>18760000</v>
       </c>
       <c r="X2" t="n">
-        <v>32242000</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>58024000</v>
+        <v>32397000</v>
       </c>
       <c r="Z2" t="n">
-        <v>45851000</v>
+        <v>18539000</v>
       </c>
       <c r="AA2" t="n">
-        <v>666000</v>
+        <v>1539000</v>
       </c>
       <c r="AB2" t="n">
-        <v>45185000</v>
+        <v>17000000</v>
       </c>
       <c r="AC2" t="n">
-        <v>5027000</v>
+        <v>6334000</v>
       </c>
       <c r="AD2" t="n">
-        <v>279000</v>
+        <v>2993000</v>
       </c>
       <c r="AE2" t="n">
-        <v>540000</v>
+        <v>2186000</v>
       </c>
       <c r="AF2" t="n">
-        <v>4208000</v>
+        <v>1155000</v>
       </c>
       <c r="AG2" t="n">
-        <v>140114000</v>
+        <v>136828000</v>
       </c>
       <c r="AH2" t="n">
-        <v>126185000</v>
+        <v>109721000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1422000</v>
+        <v>839000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6583000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>4341000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
       <c r="AL2" t="n">
-        <v>356000</v>
+        <v>2133000</v>
       </c>
       <c r="AM2" t="n">
-        <v>38000</v>
+        <v>108000</v>
       </c>
       <c r="AN2" t="n">
-        <v>38000</v>
+        <v>108000</v>
       </c>
       <c r="AO2" t="n">
-        <v>117786000</v>
+        <v>102300000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-82304000</v>
+        <v>-53074000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>200090000</v>
+        <v>155374000</v>
       </c>
       <c r="AR2" t="n">
-        <v>2842000</v>
+        <v>61367000</v>
       </c>
       <c r="AS2" t="n">
-        <v>24686000</v>
+        <v>26112000</v>
       </c>
       <c r="AT2" t="n">
-        <v>44842000</v>
+        <v>12244000</v>
       </c>
       <c r="AU2" t="n">
-        <v>127720000</v>
+        <v>55651000</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>13929000</v>
+        <v>27107000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1962000</v>
+        <v>939000</v>
       </c>
       <c r="AY2" t="n">
-        <v>3591000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>90000</v>
-      </c>
+        <v>2562000</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>3501000</v>
+        <v>2562000</v>
       </c>
       <c r="BB2" t="n">
-        <v>720000</v>
+        <v>956000</v>
       </c>
       <c r="BC2" t="n">
         <v>2561000</v>
       </c>
       <c r="BD2" t="n">
-        <v>1903000</v>
+        <v>12951000</v>
       </c>
       <c r="BE2" t="n">
-        <v>-589000</v>
+        <v>-706000</v>
       </c>
       <c r="BF2" t="n">
-        <v>2492000</v>
+        <v>13657000</v>
       </c>
       <c r="BG2" t="n">
-        <v>3192000</v>
+        <v>8077000</v>
       </c>
       <c r="BH2" t="n">
-        <v>3192000</v>
+        <v>8077000</v>
       </c>
       <c r="BI2" t="n">
-        <v>3192000</v>
+        <v>8077000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>360000000</v>
@@ -1793,43 +1793,43 @@
         <v>360000000</v>
       </c>
       <c r="D3" t="n">
-        <v>69631000</v>
+        <v>51364000</v>
       </c>
       <c r="E3" t="n">
-        <v>91505000</v>
+        <v>73606000</v>
       </c>
       <c r="F3" t="n">
-        <v>51512000</v>
+        <v>74458000</v>
       </c>
       <c r="G3" t="n">
-        <v>125627000</v>
+        <v>129334000</v>
       </c>
       <c r="H3" t="n">
-        <v>-49930000</v>
+        <v>-46553000</v>
       </c>
       <c r="I3" t="n">
-        <v>51512000</v>
+        <v>74458000</v>
       </c>
       <c r="J3" t="n">
-        <v>17436000</v>
+        <v>18791000</v>
       </c>
       <c r="K3" t="n">
-        <v>51558000</v>
+        <v>74519000</v>
       </c>
       <c r="L3" t="n">
-        <v>72058000</v>
+        <v>76319000</v>
       </c>
       <c r="M3" t="n">
-        <v>51206000</v>
+        <v>74177000</v>
       </c>
       <c r="N3" t="n">
-        <v>-352000</v>
+        <v>-342000</v>
       </c>
       <c r="O3" t="n">
-        <v>51558000</v>
+        <v>74519000</v>
       </c>
       <c r="P3" t="n">
-        <v>-18867000</v>
+        <v>4094000</v>
       </c>
       <c r="Q3" t="n">
         <v>38122000</v>
@@ -1841,131 +1841,129 @@
         <v>461000</v>
       </c>
       <c r="T3" t="n">
-        <v>106117000</v>
+        <v>84331000</v>
       </c>
       <c r="U3" t="n">
-        <v>37019000</v>
+        <v>19323000</v>
       </c>
       <c r="V3" t="n">
-        <v>37019000</v>
+        <v>19323000</v>
       </c>
       <c r="W3" t="n">
-        <v>16519000</v>
+        <v>17523000</v>
       </c>
       <c r="X3" t="n">
-        <v>20500000</v>
+        <v>1800000</v>
       </c>
       <c r="Y3" t="n">
-        <v>69098000</v>
+        <v>65008000</v>
       </c>
       <c r="Z3" t="n">
-        <v>54486000</v>
+        <v>54283000</v>
       </c>
       <c r="AA3" t="n">
-        <v>917000</v>
+        <v>1268000</v>
       </c>
       <c r="AB3" t="n">
-        <v>53569000</v>
+        <v>53015000</v>
       </c>
       <c r="AC3" t="n">
-        <v>7447000</v>
+        <v>5170000</v>
       </c>
       <c r="AD3" t="n">
-        <v>2590000</v>
+        <v>2743000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1474000</v>
+        <v>1267000</v>
       </c>
       <c r="AF3" t="n">
-        <v>3383000</v>
+        <v>1160000</v>
       </c>
       <c r="AG3" t="n">
-        <v>157323000</v>
+        <v>158508000</v>
       </c>
       <c r="AH3" t="n">
-        <v>138155000</v>
+        <v>140053000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1131000</v>
+        <v>1301000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>6583000</v>
+        <v>6490000</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>353000</v>
+        <v>2037000</v>
       </c>
       <c r="AM3" t="n">
-        <v>46000</v>
+        <v>61000</v>
       </c>
       <c r="AN3" t="n">
-        <v>46000</v>
+        <v>61000</v>
       </c>
       <c r="AO3" t="n">
-        <v>130042000</v>
+        <v>130164000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-67515000</v>
+        <v>-55220000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>197557000</v>
+        <v>185384000</v>
       </c>
       <c r="AR3" t="n">
-        <v>3057000</v>
+        <v>3094000</v>
       </c>
       <c r="AS3" t="n">
-        <v>24743000</v>
+        <v>24814000</v>
       </c>
       <c r="AT3" t="n">
-        <v>43767000</v>
+        <v>42646000</v>
       </c>
       <c r="AU3" t="n">
-        <v>125990000</v>
+        <v>114830000</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>19168000</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3059000</v>
-      </c>
+        <v>18455000</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>3131000</v>
+        <v>1435000</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>3131000</v>
+        <v>1435000</v>
       </c>
       <c r="BB3" t="n">
-        <v>400000</v>
+        <v>1733000</v>
       </c>
       <c r="BC3" t="n">
         <v>2561000</v>
       </c>
       <c r="BD3" t="n">
-        <v>5579000</v>
+        <v>9275000</v>
       </c>
       <c r="BE3" t="n">
         <v>-711000</v>
       </c>
       <c r="BF3" t="n">
-        <v>6290000</v>
+        <v>9986000</v>
       </c>
       <c r="BG3" t="n">
-        <v>4438000</v>
+        <v>3451000</v>
       </c>
       <c r="BH3" t="n">
-        <v>4438000</v>
+        <v>3451000</v>
       </c>
       <c r="BI3" t="n">
-        <v>4438000</v>
+        <v>3451000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>360000000</v>
@@ -1974,43 +1972,43 @@
         <v>360000000</v>
       </c>
       <c r="D4" t="n">
-        <v>51364000</v>
+        <v>69631000</v>
       </c>
       <c r="E4" t="n">
-        <v>73606000</v>
+        <v>91505000</v>
       </c>
       <c r="F4" t="n">
-        <v>74458000</v>
+        <v>51512000</v>
       </c>
       <c r="G4" t="n">
-        <v>129334000</v>
+        <v>125627000</v>
       </c>
       <c r="H4" t="n">
-        <v>-46553000</v>
+        <v>-49930000</v>
       </c>
       <c r="I4" t="n">
-        <v>74458000</v>
+        <v>51512000</v>
       </c>
       <c r="J4" t="n">
-        <v>18791000</v>
+        <v>17436000</v>
       </c>
       <c r="K4" t="n">
-        <v>74519000</v>
+        <v>51558000</v>
       </c>
       <c r="L4" t="n">
-        <v>76319000</v>
+        <v>72058000</v>
       </c>
       <c r="M4" t="n">
-        <v>74177000</v>
+        <v>51206000</v>
       </c>
       <c r="N4" t="n">
-        <v>-342000</v>
+        <v>-352000</v>
       </c>
       <c r="O4" t="n">
-        <v>74519000</v>
+        <v>51558000</v>
       </c>
       <c r="P4" t="n">
-        <v>4094000</v>
+        <v>-18867000</v>
       </c>
       <c r="Q4" t="n">
         <v>38122000</v>
@@ -2022,129 +2020,131 @@
         <v>461000</v>
       </c>
       <c r="T4" t="n">
-        <v>84331000</v>
+        <v>106117000</v>
       </c>
       <c r="U4" t="n">
-        <v>19323000</v>
+        <v>37019000</v>
       </c>
       <c r="V4" t="n">
-        <v>19323000</v>
+        <v>37019000</v>
       </c>
       <c r="W4" t="n">
-        <v>17523000</v>
+        <v>16519000</v>
       </c>
       <c r="X4" t="n">
-        <v>1800000</v>
+        <v>20500000</v>
       </c>
       <c r="Y4" t="n">
-        <v>65008000</v>
+        <v>69098000</v>
       </c>
       <c r="Z4" t="n">
-        <v>54283000</v>
+        <v>54486000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1268000</v>
+        <v>917000</v>
       </c>
       <c r="AB4" t="n">
-        <v>53015000</v>
+        <v>53569000</v>
       </c>
       <c r="AC4" t="n">
-        <v>5170000</v>
+        <v>7447000</v>
       </c>
       <c r="AD4" t="n">
-        <v>2743000</v>
+        <v>2590000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1267000</v>
+        <v>1474000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1160000</v>
+        <v>3383000</v>
       </c>
       <c r="AG4" t="n">
-        <v>158508000</v>
+        <v>157323000</v>
       </c>
       <c r="AH4" t="n">
-        <v>140053000</v>
+        <v>138155000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1301000</v>
+        <v>1131000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>6490000</v>
+        <v>6583000</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>2037000</v>
+        <v>353000</v>
       </c>
       <c r="AM4" t="n">
-        <v>61000</v>
+        <v>46000</v>
       </c>
       <c r="AN4" t="n">
-        <v>61000</v>
+        <v>46000</v>
       </c>
       <c r="AO4" t="n">
-        <v>130164000</v>
+        <v>130042000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-55220000</v>
+        <v>-67515000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>185384000</v>
+        <v>197557000</v>
       </c>
       <c r="AR4" t="n">
-        <v>3094000</v>
+        <v>3057000</v>
       </c>
       <c r="AS4" t="n">
-        <v>24814000</v>
+        <v>24743000</v>
       </c>
       <c r="AT4" t="n">
-        <v>42646000</v>
+        <v>43767000</v>
       </c>
       <c r="AU4" t="n">
-        <v>114830000</v>
+        <v>125990000</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>18455000</v>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+        <v>19168000</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3059000</v>
+      </c>
       <c r="AY4" t="n">
-        <v>1435000</v>
+        <v>3131000</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>1435000</v>
+        <v>3131000</v>
       </c>
       <c r="BB4" t="n">
-        <v>1733000</v>
+        <v>400000</v>
       </c>
       <c r="BC4" t="n">
         <v>2561000</v>
       </c>
       <c r="BD4" t="n">
-        <v>9275000</v>
+        <v>5579000</v>
       </c>
       <c r="BE4" t="n">
         <v>-711000</v>
       </c>
       <c r="BF4" t="n">
-        <v>9986000</v>
+        <v>6290000</v>
       </c>
       <c r="BG4" t="n">
-        <v>3451000</v>
+        <v>4438000</v>
       </c>
       <c r="BH4" t="n">
-        <v>3451000</v>
+        <v>4438000</v>
       </c>
       <c r="BI4" t="n">
-        <v>3451000</v>
+        <v>4438000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>360000000</v>
@@ -2153,43 +2153,43 @@
         <v>360000000</v>
       </c>
       <c r="D5" t="n">
-        <v>8923000</v>
+        <v>74235000</v>
       </c>
       <c r="E5" t="n">
-        <v>37299000</v>
+        <v>93963000</v>
       </c>
       <c r="F5" t="n">
-        <v>85836000</v>
+        <v>34413000</v>
       </c>
       <c r="G5" t="n">
-        <v>102944000</v>
+        <v>111878000</v>
       </c>
       <c r="H5" t="n">
-        <v>-5290000</v>
+        <v>-44095000</v>
       </c>
       <c r="I5" t="n">
-        <v>85836000</v>
+        <v>34413000</v>
       </c>
       <c r="J5" t="n">
-        <v>20299000</v>
+        <v>16536000</v>
       </c>
       <c r="K5" t="n">
-        <v>85944000</v>
+        <v>34451000</v>
       </c>
       <c r="L5" t="n">
-        <v>85944000</v>
+        <v>66693000</v>
       </c>
       <c r="M5" t="n">
-        <v>85671000</v>
+        <v>33978000</v>
       </c>
       <c r="N5" t="n">
-        <v>-273000</v>
+        <v>-473000</v>
       </c>
       <c r="O5" t="n">
-        <v>85944000</v>
+        <v>34451000</v>
       </c>
       <c r="P5" t="n">
-        <v>15519000</v>
+        <v>-37822000</v>
       </c>
       <c r="Q5" t="n">
         <v>38122000</v>
@@ -2201,128 +2201,128 @@
         <v>461000</v>
       </c>
       <c r="T5" t="n">
-        <v>51157000</v>
+        <v>106136000</v>
       </c>
       <c r="U5" t="n">
-        <v>18760000</v>
+        <v>48112000</v>
       </c>
       <c r="V5" t="n">
-        <v>18760000</v>
+        <v>48112000</v>
       </c>
       <c r="W5" t="n">
-        <v>18760000</v>
+        <v>15870000</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>32242000</v>
       </c>
       <c r="Y5" t="n">
-        <v>32397000</v>
+        <v>58024000</v>
       </c>
       <c r="Z5" t="n">
-        <v>18539000</v>
+        <v>45851000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1539000</v>
+        <v>666000</v>
       </c>
       <c r="AB5" t="n">
-        <v>17000000</v>
+        <v>45185000</v>
       </c>
       <c r="AC5" t="n">
-        <v>6334000</v>
+        <v>5027000</v>
       </c>
       <c r="AD5" t="n">
-        <v>2993000</v>
+        <v>279000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2186000</v>
+        <v>540000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1155000</v>
+        <v>4208000</v>
       </c>
       <c r="AG5" t="n">
-        <v>136828000</v>
+        <v>140114000</v>
       </c>
       <c r="AH5" t="n">
-        <v>109721000</v>
+        <v>126185000</v>
       </c>
       <c r="AI5" t="n">
-        <v>839000</v>
+        <v>1422000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4341000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
+        <v>6583000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>2133000</v>
+        <v>356000</v>
       </c>
       <c r="AM5" t="n">
-        <v>108000</v>
+        <v>38000</v>
       </c>
       <c r="AN5" t="n">
-        <v>108000</v>
+        <v>38000</v>
       </c>
       <c r="AO5" t="n">
-        <v>102300000</v>
+        <v>117786000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-53074000</v>
+        <v>-82304000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>155374000</v>
+        <v>200090000</v>
       </c>
       <c r="AR5" t="n">
-        <v>61367000</v>
+        <v>2842000</v>
       </c>
       <c r="AS5" t="n">
-        <v>26112000</v>
+        <v>24686000</v>
       </c>
       <c r="AT5" t="n">
-        <v>12244000</v>
+        <v>44842000</v>
       </c>
       <c r="AU5" t="n">
-        <v>55651000</v>
+        <v>127720000</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>27107000</v>
+        <v>13929000</v>
       </c>
       <c r="AX5" t="n">
-        <v>939000</v>
+        <v>1962000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2562000</v>
-      </c>
-      <c r="AZ5" t="inlineStr"/>
+        <v>3591000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>90000</v>
+      </c>
       <c r="BA5" t="n">
-        <v>2562000</v>
+        <v>3501000</v>
       </c>
       <c r="BB5" t="n">
-        <v>956000</v>
+        <v>720000</v>
       </c>
       <c r="BC5" t="n">
         <v>2561000</v>
       </c>
       <c r="BD5" t="n">
-        <v>12951000</v>
+        <v>1903000</v>
       </c>
       <c r="BE5" t="n">
-        <v>-706000</v>
+        <v>-589000</v>
       </c>
       <c r="BF5" t="n">
-        <v>13657000</v>
+        <v>2492000</v>
       </c>
       <c r="BG5" t="n">
-        <v>8077000</v>
+        <v>3192000</v>
       </c>
       <c r="BH5" t="n">
-        <v>8077000</v>
+        <v>3192000</v>
       </c>
       <c r="BI5" t="n">
-        <v>8077000</v>
+        <v>3192000</v>
       </c>
     </row>
   </sheetData>
@@ -2553,170 +2553,190 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-986000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-3133000</v>
-      </c>
+        <v>-45863000</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>8100000</v>
+        <v>17000000</v>
       </c>
       <c r="E2" t="n">
-        <v>-2740000</v>
+        <v>-48172000</v>
       </c>
       <c r="F2" t="n">
-        <v>3192000</v>
+        <v>8077000</v>
       </c>
       <c r="G2" t="n">
-        <v>4438000</v>
+        <v>38164000</v>
       </c>
       <c r="H2" t="n">
-        <v>-1246000</v>
+        <v>-30087000</v>
       </c>
       <c r="I2" t="n">
-        <v>-265000</v>
+        <v>15168000</v>
       </c>
       <c r="J2" t="n">
-        <v>-4392000</v>
+        <v>-1009000</v>
       </c>
       <c r="K2" t="n">
-        <v>4967000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>17000000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>17000000</v>
+      </c>
       <c r="M2" t="n">
-        <v>4967000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-3133000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>8100000</v>
+        <v>17000000</v>
       </c>
       <c r="P2" t="n">
-        <v>-2735000</v>
+        <v>-47564000</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+        <v>33000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>479000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>479000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-5000</v>
+      </c>
       <c r="W2" t="n">
-        <v>-14000</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-14000</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2726000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>-48071000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>101000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>-2726000</v>
+        <v>-48172000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1754000</v>
+        <v>2309000</v>
       </c>
       <c r="AC2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2903000</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0</v>
       </c>
-      <c r="AD2" t="n">
-        <v>1569000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>-2435000</v>
+        <v>-1282000</v>
       </c>
       <c r="AG2" t="n">
-        <v>2802000</v>
+        <v>246000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-381000</v>
+        <v>1751000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1583000</v>
+        <v>2188000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4624000</v>
+        <v>244000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-79000</v>
+        <v>344000</v>
       </c>
       <c r="AL2" t="n">
-        <v>11152000</v>
+        <v>4538000</v>
       </c>
       <c r="AM2" t="n">
-        <v>22000</v>
+        <v>121000</v>
       </c>
       <c r="AN2" t="n">
-        <v>11130000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+        <v>4417000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-86000</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>-19081000</v>
+        <v>-7191000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-12181000</v>
+        <v>-39315000</v>
       </c>
       <c r="C3" t="n">
-        <v>-367000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>19200000</v>
+        <v>37800000</v>
       </c>
       <c r="E3" t="n">
-        <v>-9115000</v>
+        <v>-32127000</v>
       </c>
       <c r="F3" t="n">
-        <v>4438000</v>
+        <v>3451000</v>
       </c>
       <c r="G3" t="n">
-        <v>3451000</v>
+        <v>8077000</v>
       </c>
       <c r="H3" t="n">
-        <v>987000</v>
+        <v>-4626000</v>
       </c>
       <c r="I3" t="n">
-        <v>13163000</v>
+        <v>34690000</v>
       </c>
       <c r="J3" t="n">
-        <v>-4463000</v>
+        <v>-2336000</v>
       </c>
       <c r="K3" t="n">
-        <v>18833000</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>37800000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>31000000</v>
+      </c>
       <c r="M3" t="n">
-        <v>18833000</v>
+        <v>37800000</v>
       </c>
       <c r="N3" t="n">
-        <v>-367000</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>19200000</v>
+        <v>37800000</v>
       </c>
       <c r="P3" t="n">
-        <v>-9110000</v>
+        <v>-32128000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2000</v>
+        <v>-2000</v>
       </c>
       <c r="R3" t="n">
-        <v>5000</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
       <c r="U3" t="n">
         <v>-2000</v>
       </c>
@@ -2724,122 +2744,120 @@
         <v>-2000</v>
       </c>
       <c r="W3" t="n">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="X3" t="n">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-9112000</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
+        <v>-32125000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
       <c r="AA3" t="n">
-        <v>-9112000</v>
+        <v>-32125000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-3066000</v>
+        <v>-7188000</v>
       </c>
       <c r="AC3" t="n">
-        <v>5000</v>
+        <v>115000</v>
       </c>
       <c r="AD3" t="n">
-        <v>5183000</v>
+        <v>932000</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>3880000</v>
+        <v>-3092000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1466000</v>
+        <v>-760000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-837000</v>
+        <v>1127000</v>
       </c>
       <c r="AI3" t="n">
-        <v>3606000</v>
+        <v>3657000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4804000</v>
+        <v>682000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-859000</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>10865000</v>
+        <v>4306000</v>
       </c>
       <c r="AM3" t="n">
-        <v>18000</v>
+        <v>49000</v>
       </c>
       <c r="AN3" t="n">
-        <v>10847000</v>
+        <v>4257000</v>
       </c>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>-23064000</v>
+        <v>-13758000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-39315000</v>
+        <v>-12181000</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-367000</v>
       </c>
       <c r="D4" t="n">
-        <v>37800000</v>
+        <v>19200000</v>
       </c>
       <c r="E4" t="n">
-        <v>-32127000</v>
+        <v>-9115000</v>
       </c>
       <c r="F4" t="n">
+        <v>4438000</v>
+      </c>
+      <c r="G4" t="n">
         <v>3451000</v>
       </c>
-      <c r="G4" t="n">
-        <v>8077000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-4626000</v>
+        <v>987000</v>
       </c>
       <c r="I4" t="n">
-        <v>34690000</v>
+        <v>13163000</v>
       </c>
       <c r="J4" t="n">
-        <v>-2336000</v>
+        <v>-4463000</v>
       </c>
       <c r="K4" t="n">
-        <v>37800000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>31000000</v>
-      </c>
+        <v>18833000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>37800000</v>
+        <v>18833000</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-367000</v>
       </c>
       <c r="O4" t="n">
-        <v>37800000</v>
+        <v>19200000</v>
       </c>
       <c r="P4" t="n">
-        <v>-32128000</v>
+        <v>-9110000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2000</v>
+        <v>2000</v>
       </c>
       <c r="R4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
+        <v>5000</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
         <v>-2000</v>
       </c>
@@ -2847,188 +2865,170 @@
         <v>-2000</v>
       </c>
       <c r="W4" t="n">
-        <v>-2000</v>
+        <v>-3000</v>
       </c>
       <c r="X4" t="n">
-        <v>-2000</v>
+        <v>-3000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-32125000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
+        <v>-9112000</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>-32125000</v>
+        <v>-9112000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-7188000</v>
+        <v>-3066000</v>
       </c>
       <c r="AC4" t="n">
-        <v>115000</v>
+        <v>5000</v>
       </c>
       <c r="AD4" t="n">
-        <v>932000</v>
+        <v>5183000</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>-3092000</v>
+        <v>3880000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-760000</v>
+        <v>-1466000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1127000</v>
+        <v>-837000</v>
       </c>
       <c r="AI4" t="n">
-        <v>3657000</v>
+        <v>3606000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>682000</v>
+        <v>4804000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-859000</v>
       </c>
       <c r="AL4" t="n">
-        <v>4306000</v>
+        <v>10865000</v>
       </c>
       <c r="AM4" t="n">
-        <v>49000</v>
+        <v>18000</v>
       </c>
       <c r="AN4" t="n">
-        <v>4257000</v>
+        <v>10847000</v>
       </c>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>-13758000</v>
+        <v>-23064000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-45863000</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>-986000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-3133000</v>
+      </c>
       <c r="D5" t="n">
-        <v>17000000</v>
+        <v>8100000</v>
       </c>
       <c r="E5" t="n">
-        <v>-48172000</v>
+        <v>-2740000</v>
       </c>
       <c r="F5" t="n">
-        <v>8077000</v>
+        <v>3192000</v>
       </c>
       <c r="G5" t="n">
-        <v>38164000</v>
+        <v>4438000</v>
       </c>
       <c r="H5" t="n">
-        <v>-30087000</v>
+        <v>-1246000</v>
       </c>
       <c r="I5" t="n">
-        <v>15168000</v>
+        <v>-265000</v>
       </c>
       <c r="J5" t="n">
-        <v>-1009000</v>
+        <v>-4392000</v>
       </c>
       <c r="K5" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>17000000</v>
-      </c>
+        <v>4967000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>4967000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-3133000</v>
+      </c>
       <c r="O5" t="n">
-        <v>17000000</v>
+        <v>8100000</v>
       </c>
       <c r="P5" t="n">
-        <v>-47564000</v>
+        <v>-2735000</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>33000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>479000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>479000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-5000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-5000</v>
-      </c>
+        <v>5000</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
+        <v>-14000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-14000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-2726000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>-2726000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1754000</v>
+      </c>
+      <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-48071000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>101000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-48172000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2309000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8000</v>
-      </c>
       <c r="AD5" t="n">
-        <v>2903000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
+        <v>1569000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>-1282000</v>
+        <v>-2435000</v>
       </c>
       <c r="AG5" t="n">
-        <v>246000</v>
+        <v>2802000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1751000</v>
+        <v>-381000</v>
       </c>
       <c r="AI5" t="n">
-        <v>2188000</v>
+        <v>1583000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>244000</v>
+        <v>4624000</v>
       </c>
       <c r="AK5" t="n">
-        <v>344000</v>
+        <v>-79000</v>
       </c>
       <c r="AL5" t="n">
-        <v>4538000</v>
+        <v>11152000</v>
       </c>
       <c r="AM5" t="n">
-        <v>121000</v>
+        <v>22000</v>
       </c>
       <c r="AN5" t="n">
-        <v>4417000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>25000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-86000</v>
-      </c>
+        <v>11130000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>-7191000</v>
+        <v>-19081000</v>
       </c>
     </row>
   </sheetData>
@@ -3618,107 +3618,107 @@
       </c>
       <c r="DK1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Dr. Siu Lin  Tan', 'age': 94, 'title': 'Founder &amp; Chairman', 'yearBorn': 1931, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Henry  Tan BBS, J.P.', 'age': 71, 'title': 'Vice Chairman of Board &amp; CEO', 'yearBorn': 1954, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Pik Shan  Cheung', 'age': 48, 'title': 'Executive Director, Group Financial Controller &amp; Company Secretary', 'yearBorn': 1977, 'fiscalYear': 2025, 'totalPay': 1356015, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. George  Chiu', 'age': 63, 'title': 'Executive Director', 'yearBorn': 1962, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sze Tink  Su Tan', 'age': 42, 'title': 'Executive VP &amp; Director', 'yearBorn': 1983, 'fiscalYear': 2025, 'totalPay': 1308849, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Maria Luisa  Ernest', 'age': 54, 'title': 'Vice President of Human Resources', 'yearBorn': 1971, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Cho Yee  Tan', 'age': 63, 'title': 'President of Guam &amp; Northern Mariana Islands', 'yearBorn': 1962, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Dr. Siu Lin  Tan', 'age': 94, 'title': 'Founder &amp; Chairman', 'yearBorn': 1931, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Henry  Tan BBS, J.P.', 'age': 71, 'title': 'Vice Chairman of Board &amp; CEO', 'yearBorn': 1954, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Pik Shan  Cheung', 'age': 48, 'title': 'Executive Director, Group Financial Controller &amp; Company Secretary', 'yearBorn': 1977, 'fiscalYear': 2025, 'totalPay': 1355962, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. George  Chiu', 'age': 63, 'title': 'Executive Director', 'yearBorn': 1962, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sze Tink  Su Tan', 'age': 42, 'title': 'Executive VP &amp; Director', 'yearBorn': 1983, 'fiscalYear': 2025, 'totalPay': 1308798, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Maria Luisa  Ernest', 'age': 54, 'title': 'Vice President of Human Resources', 'yearBorn': 1971, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Cho Yee  Tan', 'age': 63, 'title': 'President of Guam &amp; Northern Mariana Islands', 'yearBorn': 1962, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -3811,28 +3811,28 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AA2" t="n">
         <v>1591228800</v>
@@ -3841,37 +3841,37 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.299</v>
+        <v>0.339</v>
       </c>
       <c r="AD2" t="n">
-        <v>36000</v>
+        <v>12000</v>
       </c>
       <c r="AE2" t="n">
-        <v>36000</v>
+        <v>12000</v>
       </c>
       <c r="AF2" t="n">
-        <v>10933</v>
+        <v>11016</v>
       </c>
       <c r="AG2" t="n">
-        <v>25600</v>
+        <v>1200</v>
       </c>
       <c r="AH2" t="n">
-        <v>25600</v>
+        <v>1200</v>
       </c>
       <c r="AI2" t="n">
         <v>1.01</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AK2" t="n">
-        <v>403200000</v>
+        <v>385200032</v>
       </c>
       <c r="AL2" t="n">
-        <v>396000000</v>
+        <v>385200000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.42</v>
+        <v>0.435</v>
       </c>
       <c r="AN2" t="n">
         <v>1.12</v>
@@ -3883,13 +3883,13 @@
         <v>0.42</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.937359000000001</v>
+        <v>8.53837</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.7139</v>
+        <v>0.73975</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>498680992</v>
+        <v>480680992</v>
       </c>
       <c r="AY2" t="n">
         <v>-0.36749</v>
@@ -3927,10 +3927,10 @@
         <v>360000000</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.39187104</v>
+        <v>0.39185566</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.8580832</v>
+        <v>2.7305975</v>
       </c>
       <c r="BG2" t="n">
         <v>1767139200</v>
@@ -3948,16 +3948,16 @@
         <v>-0.36</v>
       </c>
       <c r="BL2" t="n">
-        <v>11.054</v>
+        <v>10.655</v>
       </c>
       <c r="BM2" t="n">
-        <v>-151.437</v>
+        <v>-145.971</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.4347825</v>
+        <v>1.4597702</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BP2" t="n">
         <v>0.0219</v>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="BS2" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
@@ -4077,11 +4077,11 @@
         <v>1557970200000</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.01999998</v>
+        <v>0</v>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>1.12 - 1.12</t>
+          <t>1.09 - 1.09</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
@@ -4090,27 +4090,27 @@
         </is>
       </c>
       <c r="CZ2" t="n">
-        <v>10933</v>
+        <v>11016</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.70000005</v>
+        <v>0.63500005</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.6666669</v>
+        <v>1.4597702</v>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>0.42 - 1.12</t>
+          <t>0.435 - 1.12</t>
         </is>
       </c>
       <c r="DD2" t="n">
-        <v>0</v>
+        <v>-0.049999952</v>
       </c>
       <c r="DE2" t="n">
-        <v>0</v>
+        <v>-0.044642814</v>
       </c>
       <c r="DF2" t="n">
-        <v>143.47826</v>
+        <v>145.97702</v>
       </c>
       <c r="DG2" t="n">
         <v>1743065658</v>
@@ -4124,86 +4124,86 @@
       <c r="DJ2" t="n">
         <v>-0.36</v>
       </c>
-      <c r="DK2" t="n">
-        <v>0.25559998</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.2956964</v>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>SAI LEISURE</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
       </c>
       <c r="DM2" t="n">
-        <v>0.40609998</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.5688471</v>
-      </c>
-      <c r="DO2" t="n">
+        <v>1781144625</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>finmb_609885415</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.12800008</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.1358812</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.33025002</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0.44643462</v>
+      </c>
+      <c r="DY2" t="n">
         <v>15</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DZ2" t="n">
         <v>15</v>
       </c>
-      <c r="DQ2" t="n">
-        <v>1.8181801</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>finmb_609885415</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DZ2" t="b">
+      <c r="EA2" t="b">
         <v>0</v>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>S.A.I. Leisure Group Company Limited</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="EB2" t="n">
-        <v>1780377135</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>SAI LEISURE</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>S.A.I. Leisure Group Company Limited</t>
-        </is>
-      </c>
-      <c r="EE2" t="b">
+      <c r="ED2" t="n">
         <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1.07</v>
       </c>
       <c r="EF2" t="inlineStr"/>
     </row>
